--- a/results/02-2025/beta/inputs-02-2025.xlsx
+++ b/results/02-2025/beta/inputs-02-2025.xlsx
@@ -35268,7 +35268,7 @@
         <v>3141.6</v>
       </c>
       <c r="P220" t="n">
-        <v>4465</v>
+        <v>4456.5</v>
       </c>
       <c r="Q220" t="n">
         <v>2477.5</v>
@@ -35325,7 +35325,7 @@
         <v>291.163</v>
       </c>
       <c r="AI220" t="n">
-        <v>-2617.53</v>
+        <v>-2616.51</v>
       </c>
       <c r="AJ220" t="n">
         <v>-1432.356</v>
@@ -35387,31 +35387,31 @@
         <v>-1</v>
       </c>
       <c r="D221" t="n">
-        <v>0.00701579758540971</v>
+        <v>0.00672681736450054</v>
       </c>
       <c r="E221" t="n">
-        <v>0.00579616682264672</v>
+        <v>0.00486028642658831</v>
       </c>
       <c r="F221" t="n">
-        <v>0.00388070534041352</v>
+        <v>0.0036140919964156</v>
       </c>
       <c r="G221" t="n">
-        <v>0.00541735421401657</v>
+        <v>0.00460786450387629</v>
       </c>
       <c r="H221" t="n">
-        <v>0.00562437877281874</v>
+        <v>0.00593953792819213</v>
       </c>
       <c r="I221" t="n">
         <v>0.00574380039423361</v>
       </c>
       <c r="J221" t="n">
-        <v>29700.6</v>
+        <v>29719.6</v>
       </c>
       <c r="K221" t="n">
-        <v>20258.4</v>
+        <v>20262.7</v>
       </c>
       <c r="L221" t="n">
-        <v>1922</v>
+        <v>1924.7</v>
       </c>
       <c r="M221" t="n">
         <v>463.5413257</v>
@@ -35420,13 +35420,13 @@
         <v>79.275</v>
       </c>
       <c r="O221" t="n">
-        <v>3174.7</v>
+        <v>3173.3</v>
       </c>
       <c r="P221" t="n">
-        <v>4526.3</v>
+        <v>4515.2</v>
       </c>
       <c r="Q221" t="n">
-        <v>2515.1</v>
+        <v>2515.7</v>
       </c>
       <c r="R221" t="n">
         <v>509.332755158353</v>
@@ -35441,7 +35441,7 @@
         <v>2171.498</v>
       </c>
       <c r="V221" t="n">
-        <v>217.8</v>
+        <v>217.7</v>
       </c>
       <c r="W221" t="n">
         <v>0</v>
@@ -35456,7 +35456,7 @@
         <v>36.1</v>
       </c>
       <c r="AA221" t="n">
-        <v>93</v>
+        <v>93.5</v>
       </c>
       <c r="AB221" t="n">
         <v>-0.901</v>
@@ -35480,10 +35480,10 @@
         <v>302.425</v>
       </c>
       <c r="AI221" t="n">
-        <v>-2624.718</v>
+        <v>-2622.366</v>
       </c>
       <c r="AJ221" t="n">
-        <v>-1449.45</v>
+        <v>-1449.522</v>
       </c>
       <c r="AK221" t="n">
         <v>-178.064425171945</v>
@@ -35495,7 +35495,7 @@
         <v>1928.338875</v>
       </c>
       <c r="AN221" t="n">
-        <v>193.5675</v>
+        <v>193.545</v>
       </c>
       <c r="AO221" t="n">
         <v>0</v>
@@ -35510,7 +35510,7 @@
         <v>31.859</v>
       </c>
       <c r="AS221" t="n">
-        <v>65.391525</v>
+        <v>65.416275</v>
       </c>
       <c r="AT221" t="n">
         <v>6.576191</v>
@@ -35554,19 +35554,19 @@
         <v>0.0075994791260281</v>
       </c>
       <c r="H222" t="n">
-        <v>0.005494147519161</v>
+        <v>0.00620657034618466</v>
       </c>
       <c r="I222" t="n">
         <v>0.00562014078474316</v>
       </c>
       <c r="J222" t="n">
-        <v>30016.3295426969</v>
+        <v>30035.5315204789</v>
       </c>
       <c r="K222" t="n">
-        <v>20476.5829790396</v>
+        <v>20480.929290042</v>
       </c>
       <c r="L222" t="n">
-        <v>1915.80213881562</v>
+        <v>1918.51028958294</v>
       </c>
       <c r="M222" t="n">
         <v>447.088159569206</v>
@@ -35575,13 +35575,13 @@
         <v>79.275</v>
       </c>
       <c r="O222" t="n">
-        <v>3204.80183566645</v>
+        <v>3203.38856116179</v>
       </c>
       <c r="P222" t="n">
-        <v>4599.01056117126</v>
+        <v>4578.84278494077</v>
       </c>
       <c r="Q222" t="n">
-        <v>2529.55898292532</v>
+        <v>2532.0824781373</v>
       </c>
       <c r="R222" t="n">
         <v>526.099889428512</v>
@@ -35593,7 +35593,7 @@
         <v>163.759599441357</v>
       </c>
       <c r="U222" t="n">
-        <v>2217.001646875</v>
+        <v>2215.99639375</v>
       </c>
       <c r="V222" t="n">
         <v>228.029047409692</v>
@@ -35611,7 +35611,7 @@
         <v>35.7</v>
       </c>
       <c r="AA222" t="n">
-        <v>93.901</v>
+        <v>94.401</v>
       </c>
       <c r="AB222" t="n">
         <v>-0.901</v>
@@ -35629,16 +35629,16 @@
         <v>0</v>
       </c>
       <c r="AG222" t="n">
-        <v>1810.01536480529</v>
+        <v>1828.47693961422</v>
       </c>
       <c r="AH222" t="n">
-        <v>305.836016607549</v>
+        <v>314.374441798612</v>
       </c>
       <c r="AI222" t="n">
-        <v>-2656.86726734055</v>
+        <v>-2652.60513419289</v>
       </c>
       <c r="AJ222" t="n">
-        <v>-1466.55107795104</v>
+        <v>-1466.92589737648</v>
       </c>
       <c r="AK222" t="n">
         <v>-182.947754819562</v>
@@ -35647,10 +35647,10 @@
         <v>-65.2294783030734</v>
       </c>
       <c r="AM222" t="n">
-        <v>1952.12197054688</v>
+        <v>1951.89578859375</v>
       </c>
       <c r="AN222" t="n">
-        <v>197.916535667181</v>
+        <v>197.894035667181</v>
       </c>
       <c r="AO222" t="n">
         <v>0</v>
@@ -35665,7 +35665,7 @@
         <v>32.173</v>
       </c>
       <c r="AS222" t="n">
-        <v>60.4834245</v>
+        <v>60.5295495</v>
       </c>
       <c r="AT222" t="n">
         <v>4.63454</v>
@@ -35680,10 +35680,10 @@
         <v>0.35145</v>
       </c>
       <c r="AX222" t="n">
-        <v>1577.33648208119</v>
+        <v>1581.4903364132</v>
       </c>
       <c r="AY222" t="n">
-        <v>269.092578736699</v>
+        <v>271.013724404688</v>
       </c>
     </row>
     <row r="223">
@@ -35709,19 +35709,19 @@
         <v>0.00707611529348728</v>
       </c>
       <c r="H223" t="n">
-        <v>0.00532817330872071</v>
+        <v>0.00557412911254063</v>
       </c>
       <c r="I223" t="n">
         <v>0.00571780133544419</v>
       </c>
       <c r="J223" t="n">
-        <v>30325.5522939305</v>
+        <v>30344.9520869847</v>
       </c>
       <c r="K223" t="n">
-        <v>20716.5441119208</v>
+        <v>20720.9413565049</v>
       </c>
       <c r="L223" t="n">
-        <v>1915.49537974805</v>
+        <v>1918.21157840012</v>
       </c>
       <c r="M223" t="n">
         <v>442.796289684976</v>
@@ -35730,13 +35730,13 @@
         <v>75.203</v>
       </c>
       <c r="O223" t="n">
-        <v>3231.06115711615</v>
+        <v>3229.63630260393</v>
       </c>
       <c r="P223" t="n">
-        <v>4622.15249842381</v>
+        <v>4601.87789173116</v>
       </c>
       <c r="Q223" t="n">
-        <v>2561.00840480961</v>
+        <v>2563.56513203677</v>
       </c>
       <c r="R223" t="n">
         <v>543.418994465887</v>
@@ -35748,7 +35748,7 @@
         <v>163.691956140612</v>
       </c>
       <c r="U223" t="n">
-        <v>2223.701646875</v>
+        <v>2222.69639375</v>
       </c>
       <c r="V223" t="n">
         <v>231.362463474923</v>
@@ -35766,7 +35766,7 @@
         <v>35.7</v>
       </c>
       <c r="AA223" t="n">
-        <v>85.879</v>
+        <v>86.379</v>
       </c>
       <c r="AB223" t="n">
         <v>-0.901</v>
@@ -35784,16 +35784,16 @@
         <v>0</v>
       </c>
       <c r="AG223" t="n">
-        <v>1838.09929820175</v>
+        <v>1856.9365023439</v>
       </c>
       <c r="AH223" t="n">
-        <v>312.082297057302</v>
+        <v>320.795107851913</v>
       </c>
       <c r="AI223" t="n">
-        <v>-2687.19756715141</v>
+        <v>-2681.16848120063</v>
       </c>
       <c r="AJ223" t="n">
-        <v>-1484.27608652819</v>
+        <v>-1484.92171322089</v>
       </c>
       <c r="AK223" t="n">
         <v>-187.158387968425</v>
@@ -35802,10 +35802,10 @@
         <v>-65.4325435077605</v>
       </c>
       <c r="AM223" t="n">
-        <v>1971.99006609375</v>
+        <v>1971.5377021875</v>
       </c>
       <c r="AN223" t="n">
-        <v>202.228089949038</v>
+        <v>202.205589949038</v>
       </c>
       <c r="AO223" t="n">
         <v>0</v>
@@ -35820,7 +35820,7 @@
         <v>32.379</v>
       </c>
       <c r="AS223" t="n">
-        <v>52.84992825</v>
+        <v>52.91630325</v>
       </c>
       <c r="AT223" t="n">
         <v>2.745007</v>
@@ -35835,10 +35835,10 @@
         <v>0.250425</v>
       </c>
       <c r="AX223" t="n">
-        <v>1609.47599917658</v>
+        <v>1617.86822444058</v>
       </c>
       <c r="AY223" t="n">
-        <v>272.588920574591</v>
+        <v>276.470448671368</v>
       </c>
     </row>
     <row r="224">
@@ -35864,19 +35864,19 @@
         <v>0.00774551207611962</v>
       </c>
       <c r="H224" t="n">
-        <v>0.00520298538473263</v>
+        <v>0.00542443641023826</v>
       </c>
       <c r="I224" t="n">
         <v>0.00573662843673683</v>
       </c>
       <c r="J224" t="n">
-        <v>30628.0680447326</v>
+        <v>30647.661362472</v>
       </c>
       <c r="K224" t="n">
-        <v>20921.8809909986</v>
+        <v>20926.3218199022</v>
       </c>
       <c r="L224" t="n">
-        <v>1921.04530428972</v>
+        <v>1923.76937281071</v>
       </c>
       <c r="M224" t="n">
         <v>445.709739995982</v>
@@ -35885,13 +35885,13 @@
         <v>75.203</v>
       </c>
       <c r="O224" t="n">
-        <v>3260.58967717546</v>
+        <v>3259.15180098305</v>
       </c>
       <c r="P224" t="n">
-        <v>4645.50799100346</v>
+        <v>4625.12586957864</v>
       </c>
       <c r="Q224" t="n">
-        <v>2588.01712691122</v>
+        <v>2590.60267019395</v>
       </c>
       <c r="R224" t="n">
         <v>561.308241039732</v>
@@ -35903,7 +35903,7 @@
         <v>163.832074406442</v>
       </c>
       <c r="U224" t="n">
-        <v>2230.401646875</v>
+        <v>2229.39639375</v>
       </c>
       <c r="V224" t="n">
         <v>234.744608694576</v>
@@ -35921,7 +35921,7 @@
         <v>35.7</v>
       </c>
       <c r="AA224" t="n">
-        <v>85.879</v>
+        <v>86.379</v>
       </c>
       <c r="AB224" t="n">
         <v>-0.901</v>
@@ -35939,16 +35939,16 @@
         <v>0</v>
       </c>
       <c r="AG224" t="n">
-        <v>1867.77658566197</v>
+        <v>1887.0287015469</v>
       </c>
       <c r="AH224" t="n">
-        <v>317.322854174324</v>
+        <v>326.181972475158</v>
       </c>
       <c r="AI224" t="n">
-        <v>-2713.67589240155</v>
+        <v>-2706.41101845362</v>
       </c>
       <c r="AJ224" t="n">
-        <v>-1502.02260278202</v>
+        <v>-1502.82708495593</v>
       </c>
       <c r="AK224" t="n">
         <v>-192.461996003083</v>
@@ -35957,10 +35957,10 @@
         <v>-65.5902793213086</v>
       </c>
       <c r="AM224" t="n">
-        <v>1989.58566164063</v>
+        <v>1988.90711578125</v>
       </c>
       <c r="AN224" t="n">
-        <v>205.185626905318</v>
+        <v>205.163126905318</v>
       </c>
       <c r="AO224" t="n">
         <v>0</v>
@@ -35975,7 +35975,7 @@
         <v>32.451</v>
       </c>
       <c r="AS224" t="n">
-        <v>46.79247825</v>
+        <v>46.87797825</v>
       </c>
       <c r="AT224" t="n">
         <v>0.855474</v>
@@ -35990,10 +35990,10 @@
         <v>0.222075</v>
       </c>
       <c r="AX224" t="n">
-        <v>1640.15240595052</v>
+        <v>1652.87635728863</v>
       </c>
       <c r="AY224" t="n">
-        <v>278.474887763814</v>
+        <v>284.349717478279</v>
       </c>
     </row>
     <row r="225">
@@ -36019,19 +36019,19 @@
         <v>0.00800202664149885</v>
       </c>
       <c r="H225" t="n">
-        <v>0.00523657192280469</v>
+        <v>0.00545800076174396</v>
       </c>
       <c r="I225" t="n">
         <v>0.00571666765914358</v>
       </c>
       <c r="J225" t="n">
-        <v>30921.5743919702</v>
+        <v>30941.3554709197</v>
       </c>
       <c r="K225" t="n">
-        <v>21120.0922990037</v>
+        <v>21124.5751997701</v>
       </c>
       <c r="L225" t="n">
-        <v>1926.83504223656</v>
+        <v>1929.56732068516</v>
       </c>
       <c r="M225" t="n">
         <v>444.7661988</v>
@@ -36040,13 +36040,13 @@
         <v>75.203</v>
       </c>
       <c r="O225" t="n">
-        <v>3291.22060203007</v>
+        <v>3289.76921801178</v>
       </c>
       <c r="P225" t="n">
-        <v>4669.0771571723</v>
+        <v>4648.58683405003</v>
       </c>
       <c r="Q225" t="n">
-        <v>2614.62275452149</v>
+        <v>2617.237284825</v>
       </c>
       <c r="R225" t="n">
         <v>557.839987860135</v>
@@ -36058,7 +36058,7 @@
         <v>163.749936112679</v>
       </c>
       <c r="U225" t="n">
-        <v>2220.862646875</v>
+        <v>2219.85739375</v>
       </c>
       <c r="V225" t="n">
         <v>238.176195410118</v>
@@ -36076,7 +36076,7 @@
         <v>35.7</v>
       </c>
       <c r="AA225" t="n">
-        <v>90.218</v>
+        <v>90.718</v>
       </c>
       <c r="AB225" t="n">
         <v>-2.15</v>
@@ -36094,16 +36094,16 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>1894.69433654438</v>
+        <v>1914.20570616006</v>
       </c>
       <c r="AH225" t="n">
-        <v>322.667165556127</v>
+        <v>331.675488007072</v>
       </c>
       <c r="AI225" t="n">
-        <v>-2739.3740013568</v>
+        <v>-2730.86676503576</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-1519.36482903602</v>
+        <v>-1520.32965121272</v>
       </c>
       <c r="AK225" t="n">
         <v>-197.493328931754</v>
@@ -36112,7 +36112,7 @@
         <v>-65.6419438583979</v>
       </c>
       <c r="AM225" t="n">
-        <v>2000.6927071875</v>
+        <v>1999.787979375</v>
       </c>
       <c r="AN225" t="n">
         <v>209.770270872594</v>
@@ -36130,7 +36130,7 @@
         <v>32.451</v>
       </c>
       <c r="AS225" t="n">
-        <v>43.473006</v>
+        <v>43.575381</v>
       </c>
       <c r="AT225" t="n">
         <v>0.573855</v>
@@ -36145,10 +36145,10 @@
         <v>0.1953</v>
       </c>
       <c r="AX225" t="n">
-        <v>1667.38175667301</v>
+        <v>1684.49576617464</v>
       </c>
       <c r="AY225" t="n">
-        <v>283.029375013943</v>
+        <v>290.93107727987</v>
       </c>
     </row>
     <row r="226">
@@ -36174,19 +36174,19 @@
         <v>0.00818999490559191</v>
       </c>
       <c r="H226" t="n">
-        <v>0.00510308766890821</v>
+        <v>0.0053246047022768</v>
       </c>
       <c r="I226" t="n">
         <v>0.00567994383495618</v>
       </c>
       <c r="J226" t="n">
-        <v>31224.7908741608</v>
+        <v>31244.7659260657</v>
       </c>
       <c r="K226" t="n">
-        <v>21300.8409398733</v>
+        <v>21305.3622059181</v>
       </c>
       <c r="L226" t="n">
-        <v>1936.90542286818</v>
+        <v>1939.65198125428</v>
       </c>
       <c r="M226" t="n">
         <v>447.863487871975</v>
@@ -36195,13 +36195,13 @@
         <v>75.203</v>
       </c>
       <c r="O226" t="n">
-        <v>3322.72316165216</v>
+        <v>3321.25788542879</v>
       </c>
       <c r="P226" t="n">
-        <v>4788.29147684674</v>
+        <v>4767.14761837742</v>
       </c>
       <c r="Q226" t="n">
-        <v>2639.09180766924</v>
+        <v>2641.73325967196</v>
       </c>
       <c r="R226" t="n">
         <v>554.393164581683</v>
@@ -36213,7 +36213,7 @@
         <v>163.948034350578</v>
       </c>
       <c r="U226" t="n">
-        <v>2267.96985716788</v>
+        <v>2263.55853501175</v>
       </c>
       <c r="V226" t="n">
         <v>241.657946376297</v>
@@ -36231,7 +36231,7 @@
         <v>35.7</v>
       </c>
       <c r="AA226" t="n">
-        <v>88.068</v>
+        <v>88.568</v>
       </c>
       <c r="AB226" t="n">
         <v>0</v>
@@ -36249,16 +36249,16 @@
         <v>0</v>
       </c>
       <c r="AG226" t="n">
-        <v>1922.73211492331</v>
+        <v>1942.52664111013</v>
       </c>
       <c r="AH226" t="n">
-        <v>327.367887749924</v>
+        <v>336.507446427527</v>
       </c>
       <c r="AI226" t="n">
-        <v>-2771.3944991182</v>
+        <v>-2761.57292706633</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-1537.05681834166</v>
+        <v>-1538.18348216172</v>
       </c>
       <c r="AK226" t="n">
         <v>-201.49643441781</v>
@@ -36267,7 +36267,7 @@
         <v>-65.8168783367505</v>
       </c>
       <c r="AM226" t="n">
-        <v>2012.1605545034</v>
+        <v>2010.48946115889</v>
       </c>
       <c r="AN226" t="n">
         <v>212.83677314008</v>
@@ -36285,7 +36285,7 @@
         <v>32.475</v>
       </c>
       <c r="AS226" t="n">
-        <v>42.5401155</v>
+        <v>42.6593655</v>
       </c>
       <c r="AT226" t="n">
         <v>0.378236</v>
@@ -36300,10 +36300,10 @@
         <v>0.171675</v>
       </c>
       <c r="AX226" t="n">
-        <v>1692.74302544956</v>
+        <v>1710.15694901122</v>
       </c>
       <c r="AY226" t="n">
-        <v>287.874046020977</v>
+        <v>295.911003321376</v>
       </c>
     </row>
     <row r="227">
@@ -36335,13 +36335,13 @@
         <v>0.0056310426470525</v>
       </c>
       <c r="J227" t="n">
-        <v>31527.1064159948</v>
+        <v>31547.2748645078</v>
       </c>
       <c r="K227" t="n">
-        <v>21496.1418033558</v>
+        <v>21500.7045234993</v>
       </c>
       <c r="L227" t="n">
-        <v>1947.35251893945</v>
+        <v>1950.11389145069</v>
       </c>
       <c r="M227" t="n">
         <v>448.188295792375</v>
@@ -36350,13 +36350,13 @@
         <v>75.203</v>
       </c>
       <c r="O227" t="n">
-        <v>3352.0947052084</v>
+        <v>3350.61647652938</v>
       </c>
       <c r="P227" t="n">
-        <v>4821.14923693197</v>
+        <v>4799.87138609857</v>
       </c>
       <c r="Q227" t="n">
-        <v>2664.54486008583</v>
+        <v>2667.21316119132</v>
       </c>
       <c r="R227" t="n">
         <v>550.967638791707</v>
@@ -36368,7 +36368,7 @@
         <v>164.27175586129</v>
       </c>
       <c r="U227" t="n">
-        <v>2273.94185716788</v>
+        <v>2269.53053501175</v>
       </c>
       <c r="V227" t="n">
         <v>245.190594913367</v>
@@ -36386,7 +36386,7 @@
         <v>35.7</v>
       </c>
       <c r="AA227" t="n">
-        <v>88.068</v>
+        <v>88.568</v>
       </c>
       <c r="AB227" t="n">
         <v>0</v>
@@ -36404,16 +36404,16 @@
         <v>0</v>
       </c>
       <c r="AG227" t="n">
-        <v>1951.29278518874</v>
+        <v>1971.37758953044</v>
       </c>
       <c r="AH227" t="n">
-        <v>332.029193803636</v>
+        <v>341.298888275819</v>
       </c>
       <c r="AI227" t="n">
-        <v>-2804.75577811969</v>
+        <v>-2793.61028335515</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-1553.58483628067</v>
+        <v>-1554.87482441518</v>
       </c>
       <c r="AK227" t="n">
         <v>-205.5486890442</v>
@@ -36422,7 +36422,7 @@
         <v>-65.8792701987935</v>
       </c>
       <c r="AM227" t="n">
-        <v>2023.46460181929</v>
+        <v>2021.02714294279</v>
       </c>
       <c r="AN227" t="n">
         <v>215.94810271373</v>
@@ -36440,7 +36440,7 @@
         <v>32.507</v>
       </c>
       <c r="AS227" t="n">
-        <v>41.89377375</v>
+        <v>42.02989875</v>
       </c>
       <c r="AT227" t="n">
         <v>0.211344</v>
@@ -36455,10 +36455,10 @@
         <v>0.14805</v>
       </c>
       <c r="AX227" t="n">
-        <v>1718.21156002164</v>
+        <v>1735.90619362819</v>
       </c>
       <c r="AY227" t="n">
-        <v>292.362097788902</v>
+        <v>300.524353916754</v>
       </c>
     </row>
     <row r="228">
@@ -36490,13 +36490,13 @@
         <v>0.00558696597638098</v>
       </c>
       <c r="J228" t="n">
-        <v>31822.8150618815</v>
+        <v>31843.1726804541</v>
       </c>
       <c r="K228" t="n">
-        <v>21666.8544286302</v>
+        <v>21671.4533838311</v>
       </c>
       <c r="L228" t="n">
-        <v>1958.55020912426</v>
+        <v>1961.32746011336</v>
       </c>
       <c r="M228" t="n">
         <v>452.346923275822</v>
@@ -36505,13 +36505,13 @@
         <v>75.203</v>
       </c>
       <c r="O228" t="n">
-        <v>3382.01967066365</v>
+        <v>3380.52824547736</v>
       </c>
       <c r="P228" t="n">
-        <v>4854.37939110322</v>
+        <v>4832.96643578863</v>
       </c>
       <c r="Q228" t="n">
-        <v>2687.78303814039</v>
+        <v>2690.47705353563</v>
       </c>
       <c r="R228" t="n">
         <v>547.563278895698</v>
@@ -36523,7 +36523,7 @@
         <v>164.107479273765</v>
       </c>
       <c r="U228" t="n">
-        <v>2281.64185716788</v>
+        <v>2277.23053501175</v>
       </c>
       <c r="V228" t="n">
         <v>248.77488506154</v>
@@ -36541,7 +36541,7 @@
         <v>35.7</v>
       </c>
       <c r="AA228" t="n">
-        <v>88.068</v>
+        <v>88.568</v>
       </c>
       <c r="AB228" t="n">
         <v>0</v>
@@ -36559,16 +36559,16 @@
         <v>0</v>
       </c>
       <c r="AG228" t="n">
-        <v>1980.30627373342</v>
+        <v>2000.68640958851</v>
       </c>
       <c r="AH228" t="n">
-        <v>336.728298734213</v>
+        <v>346.129184281796</v>
       </c>
       <c r="AI228" t="n">
-        <v>-2832.08381644128</v>
+        <v>-2820.14739854715</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-1569.12329239736</v>
+        <v>-1570.57807525913</v>
       </c>
       <c r="AK228" t="n">
         <v>-208.73746500739</v>
@@ -36577,7 +36577,7 @@
         <v>-65.819519507919</v>
       </c>
       <c r="AM228" t="n">
-        <v>2034.99364913519</v>
+        <v>2031.78982472668</v>
       </c>
       <c r="AN228" t="n">
         <v>219.104914896297</v>
@@ -36595,7 +36595,7 @@
         <v>32.503</v>
       </c>
       <c r="AS228" t="n">
-        <v>41.31180675</v>
+        <v>41.46480675</v>
       </c>
       <c r="AT228" t="n">
         <v>-0.00499800000000003</v>
@@ -36610,10 +36610,10 @@
         <v>0.124425</v>
       </c>
       <c r="AX228" t="n">
-        <v>1743.53073983771</v>
+        <v>1761.47917793756</v>
       </c>
       <c r="AY228" t="n">
-        <v>296.728322814877</v>
+        <v>305.012476573248</v>
       </c>
     </row>
     <row r="229">
@@ -36645,13 +36645,13 @@
         <v>0.00554760795794795</v>
       </c>
       <c r="J229" t="n">
-        <v>32120.025275029</v>
+        <v>32140.5730242403</v>
       </c>
       <c r="K229" t="n">
-        <v>21860.2484491496</v>
+        <v>21864.8884537073</v>
       </c>
       <c r="L229" t="n">
-        <v>1968.55010329008</v>
+        <v>1971.34153426591</v>
       </c>
       <c r="M229" t="n">
         <v>454.536674</v>
@@ -36660,13 +36660,13 @@
         <v>75.203</v>
       </c>
       <c r="O229" t="n">
-        <v>3411.2234432123</v>
+        <v>3409.71913955511</v>
       </c>
       <c r="P229" t="n">
-        <v>4887.98436710034</v>
+        <v>4866.43518654803</v>
       </c>
       <c r="Q229" t="n">
-        <v>2712.94914769761</v>
+        <v>2715.66964953021</v>
       </c>
       <c r="R229" t="n">
         <v>544.179954112255</v>
@@ -36678,7 +36678,7 @@
         <v>164.305577511663</v>
       </c>
       <c r="U229" t="n">
-        <v>2289.34185716788</v>
+        <v>2284.93053501175</v>
       </c>
       <c r="V229" t="n">
         <v>252.41157173769</v>
@@ -36696,7 +36696,7 @@
         <v>35.7</v>
       </c>
       <c r="AA229" t="n">
-        <v>88.068</v>
+        <v>88.568</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -36714,16 +36714,16 @@
         <v>0</v>
       </c>
       <c r="AG229" t="n">
-        <v>2009.80875491517</v>
+        <v>2030.48566595013</v>
       </c>
       <c r="AH229" t="n">
-        <v>341.838102087878</v>
+        <v>351.381644717384</v>
       </c>
       <c r="AI229" t="n">
-        <v>-2857.7949862774</v>
+        <v>-2845.21533776699</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-1583.89849851592</v>
+        <v>-1585.48364353128</v>
       </c>
       <c r="AK229" t="n">
         <v>-211.383463477799</v>
@@ -36732,7 +36732,7 @@
         <v>-65.7330387583077</v>
       </c>
       <c r="AM229" t="n">
-        <v>2050.40147145109</v>
+        <v>2046.43128151058</v>
       </c>
       <c r="AN229" t="n">
         <v>222.307874570001</v>
@@ -36750,7 +36750,7 @@
         <v>32.487</v>
       </c>
       <c r="AS229" t="n">
-        <v>40.86927675</v>
+        <v>41.03577675</v>
       </c>
       <c r="AT229" t="n">
         <v>-0.028203</v>
@@ -36765,10 +36765,10 @@
         <v>0.1008</v>
       </c>
       <c r="AX229" t="n">
-        <v>1769.43148397114</v>
+        <v>1787.64216889032</v>
       </c>
       <c r="AY229" t="n">
-        <v>301.041783534522</v>
+        <v>309.446361833068</v>
       </c>
     </row>
     <row r="230">
@@ -36800,10 +36800,10 @@
         <v>0.00550459474437348</v>
       </c>
       <c r="J230" t="n">
-        <v>32424.8434289643</v>
+        <v>32445.5861757489</v>
       </c>
       <c r="K230" t="n">
-        <v>22065.9867688512</v>
+        <v>22070.6704429373</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -36875,10 +36875,10 @@
         <v>0</v>
       </c>
       <c r="AI230" t="n">
-        <v>-2290.59158914093</v>
+        <v>-2280.50678452323</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-1270.85797725198</v>
+        <v>-1272.1300716309</v>
       </c>
       <c r="AK230" t="n">
         <v>-196.053463477799</v>
@@ -36887,7 +36887,7 @@
         <v>-60.0530387583078</v>
       </c>
       <c r="AM230" t="n">
-        <v>1540.10825358832</v>
+        <v>1537.13061113293</v>
       </c>
       <c r="AN230" t="n">
         <v>167.934836635334</v>
@@ -36905,7 +36905,7 @@
         <v>25.347</v>
       </c>
       <c r="AS230" t="n">
-        <v>36.184374</v>
+        <v>36.339624</v>
       </c>
       <c r="AT230" t="n">
         <v>-0.051408</v>
@@ -36920,10 +36920,10 @@
         <v>0.0819</v>
       </c>
       <c r="AX230" t="n">
-        <v>1336.8167581134</v>
+        <v>1350.57367464054</v>
       </c>
       <c r="AY230" t="n">
-        <v>227.384008790789</v>
+        <v>233.732186386875</v>
       </c>
     </row>
     <row r="231">
@@ -36955,10 +36955,10 @@
         <v>0.00545389484594594</v>
       </c>
       <c r="J231" t="n">
-        <v>32721.5531196915</v>
+        <v>32742.4856769218</v>
       </c>
       <c r="K231" t="n">
-        <v>22249.5454940874</v>
+        <v>22254.2681299138</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -37030,10 +37030,10 @@
         <v>0</v>
       </c>
       <c r="AI231" t="n">
-        <v>-1719.98337720948</v>
+        <v>-1712.40799982648</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-954.420524101547</v>
+        <v>-955.375984736884</v>
       </c>
       <c r="AK231" t="n">
         <v>-179.606796811132</v>
@@ -37042,7 +37042,7 @@
         <v>-54.5863720916411</v>
       </c>
       <c r="AM231" t="n">
-        <v>1028.47133572554</v>
+        <v>1026.48624075529</v>
       </c>
       <c r="AN231" t="n">
         <v>112.766952779827</v>
@@ -37060,7 +37060,7 @@
         <v>19.278</v>
       </c>
       <c r="AS231" t="n">
-        <v>32.20927875</v>
+        <v>32.35665375</v>
       </c>
       <c r="AT231" t="n">
         <v>-0.074613</v>
@@ -37075,10 +37075,10 @@
         <v>0.063</v>
       </c>
       <c r="AX231" t="n">
-        <v>897.775881445933</v>
+        <v>907.013716996196</v>
       </c>
       <c r="AY231" t="n">
-        <v>152.677440184971</v>
+        <v>156.939936524816</v>
       </c>
     </row>
     <row r="232">
@@ -37110,10 +37110,10 @@
         <v>0.00542022049047874</v>
       </c>
       <c r="J232" t="n">
-        <v>33021.8665718446</v>
+        <v>33042.9912449106</v>
       </c>
       <c r="K232" t="n">
-        <v>22433.6060201033</v>
+        <v>22438.367724181</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -37185,10 +37185,10 @@
         <v>0</v>
       </c>
       <c r="AI232" t="n">
-        <v>-1441.25289774927</v>
+        <v>-1434.90044765176</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-799.139496486874</v>
+        <v>-799.939824525247</v>
       </c>
       <c r="AK232" t="n">
         <v>-163.170130144465</v>
@@ -37197,7 +37197,7 @@
         <v>-49.1663720916411</v>
       </c>
       <c r="AM232" t="n">
-        <v>515.101917862772</v>
+        <v>514.109370377644</v>
       </c>
       <c r="AN232" t="n">
         <v>56.7926036409802</v>
@@ -37215,7 +37215,7 @@
         <v>13.566</v>
       </c>
       <c r="AS232" t="n">
-        <v>28.4413365</v>
+        <v>28.5819615</v>
       </c>
       <c r="AT232" t="n">
         <v>-0.097818</v>
@@ -37230,10 +37230,10 @@
         <v>0.0441</v>
       </c>
       <c r="AX232" t="n">
-        <v>452.206969855913</v>
+        <v>456.85927483878</v>
       </c>
       <c r="AY232" t="n">
-        <v>76.9135729697727</v>
+        <v>79.0608700614115</v>
       </c>
     </row>
     <row r="233">
@@ -37265,10 +37265,10 @@
         <v>0.00537879404345354</v>
       </c>
       <c r="J233" t="n">
-        <v>33332.8912037911</v>
+        <v>33354.2148448243</v>
       </c>
       <c r="K233" t="n">
-        <v>22630.9140867049</v>
+        <v>22635.7176709255</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -37340,10 +37340,10 @@
         <v>0</v>
       </c>
       <c r="AI233" t="n">
-        <v>-1161.10826831894</v>
+        <v>-1155.98523760876</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-642.262131215584</v>
+        <v>-642.905587435747</v>
       </c>
       <c r="AK233" t="n">
         <v>-146.192371639187</v>
@@ -37370,7 +37370,7 @@
         <v>8.211</v>
       </c>
       <c r="AS233" t="n">
-        <v>24.871959</v>
+        <v>24.997959</v>
       </c>
       <c r="AT233" t="n">
         <v>-0.082501</v>
@@ -37420,10 +37420,10 @@
         <v>0.00534192357811758</v>
       </c>
       <c r="J234" t="n">
-        <v>33646.5185523229</v>
+        <v>33668.0428263273</v>
       </c>
       <c r="K234" t="n">
-        <v>22838.2581689017</v>
+        <v>22843.105763486</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -37495,10 +37495,10 @@
         <v>0</v>
       </c>
       <c r="AI234" t="n">
-        <v>-873.810779708131</v>
+        <v>-869.956380506113</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-483.91662275543</v>
+        <v>-484.40159185543</v>
       </c>
       <c r="AK234" t="n">
         <v>-128.655708658236</v>
@@ -37525,7 +37525,7 @@
         <v>4.998</v>
       </c>
       <c r="AS234" t="n">
-        <v>21.722382</v>
+        <v>21.836007</v>
       </c>
       <c r="AT234" t="n">
         <v>-0.067184</v>
@@ -37575,10 +37575,10 @@
         <v>0.00532158987529296</v>
       </c>
       <c r="J235" t="n">
-        <v>33952.5379600669</v>
+        <v>33974.2580001079</v>
       </c>
       <c r="K235" t="n">
-        <v>23043.1936073557</v>
+        <v>23048.0847010507</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -37650,10 +37650,10 @@
         <v>0</v>
       </c>
       <c r="AI235" t="n">
-        <v>-584.541825492213</v>
+        <v>-581.964097340199</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-324.04393115028</v>
+        <v>-324.36880218395</v>
       </c>
       <c r="AK235" t="n">
         <v>-110.54174217604</v>
@@ -37680,7 +37680,7 @@
         <v>3.213</v>
       </c>
       <c r="AS235" t="n">
-        <v>18.738801</v>
+        <v>18.840051</v>
       </c>
       <c r="AT235" t="n">
         <v>-0.051867</v>
@@ -37730,10 +37730,10 @@
         <v>0.00528941636235492</v>
       </c>
       <c r="J236" t="n">
-        <v>34267.3665624073</v>
+        <v>34289.2880038828</v>
       </c>
       <c r="K236" t="n">
-        <v>23259.1686629644</v>
+        <v>23264.1055990132</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -37805,10 +37805,10 @@
         <v>0</v>
       </c>
       <c r="AI236" t="n">
-        <v>-293.27906202602</v>
+        <v>-291.986111192882</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-162.776948861856</v>
+        <v>-162.940178971813</v>
       </c>
       <c r="AK236" t="n">
         <v>-91.8314674747158</v>
@@ -37835,7 +37835,7 @@
         <v>1.428</v>
       </c>
       <c r="AS236" t="n">
-        <v>15.76962</v>
+        <v>15.858495</v>
       </c>
       <c r="AT236" t="n">
         <v>-0.03655</v>
@@ -37885,10 +37885,10 @@
         <v>0.00524963654830413</v>
       </c>
       <c r="J237" t="n">
-        <v>34589.5027920835</v>
+        <v>34611.6303098121</v>
       </c>
       <c r="K237" t="n">
-        <v>23479.0577646552</v>
+        <v>23484.0413738439</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -37990,7 +37990,7 @@
         <v>0</v>
       </c>
       <c r="AS237" t="n">
-        <v>12.714237</v>
+        <v>12.786237</v>
       </c>
       <c r="AT237" t="n">
         <v>0</v>
@@ -38040,10 +38040,10 @@
         <v>0.00521033508596069</v>
       </c>
       <c r="J238" t="n">
-        <v>34917.1447683825</v>
+        <v>34939.4818844878</v>
       </c>
       <c r="K238" t="n">
-        <v>23708.8825217852</v>
+        <v>23713.9149130325</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -38145,7 +38145,7 @@
         <v>0</v>
       </c>
       <c r="AS238" t="n">
-        <v>10.283904</v>
+        <v>10.342404</v>
       </c>
       <c r="AT238" t="n">
         <v>0</v>
@@ -38195,10 +38195,10 @@
         <v>0.00516756143130825</v>
       </c>
       <c r="J239" t="n">
-        <v>35247.889983687</v>
+        <v>35270.4386833661</v>
       </c>
       <c r="K239" t="n">
-        <v>23944.2270874926</v>
+        <v>23949.30943242</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -38300,7 +38300,7 @@
         <v>0</v>
       </c>
       <c r="AS239" t="n">
-        <v>7.925769</v>
+        <v>7.970769</v>
       </c>
       <c r="AT239" t="n">
         <v>0</v>
@@ -38350,10 +38350,10 @@
         <v>0.00510570215168871</v>
       </c>
       <c r="J240" t="n">
-        <v>35580.5371841885</v>
+        <v>35603.2986841751</v>
       </c>
       <c r="K240" t="n">
-        <v>24176.6612086774</v>
+        <v>24181.7928895208</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -38455,7 +38455,7 @@
         <v>0</v>
       </c>
       <c r="AS240" t="n">
-        <v>5.567634</v>
+        <v>5.599134</v>
       </c>
       <c r="AT240" t="n">
         <v>0</v>
@@ -38505,10 +38505,10 @@
         <v>0.00504465278509314</v>
       </c>
       <c r="J241" t="n">
-        <v>35915.6869967913</v>
+        <v>35938.6628980505</v>
       </c>
       <c r="K241" t="n">
-        <v>24411.9054142289</v>
+        <v>24417.0870274501</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -38610,7 +38610,7 @@
         <v>0</v>
       </c>
       <c r="AS241" t="n">
-        <v>3.170448</v>
+        <v>3.188448</v>
       </c>
       <c r="AT241" t="n">
         <v>0</v>
@@ -38660,10 +38660,10 @@
         <v>0.00499215850685553</v>
       </c>
       <c r="J242" t="n">
-        <v>36257.5438098255</v>
+        <v>36280.7384029444</v>
       </c>
       <c r="K242" t="n">
-        <v>24655.8809533482</v>
+        <v>24661.1143522394</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -38765,7 +38765,7 @@
         <v>0</v>
       </c>
       <c r="AS242" t="n">
-        <v>2.377836</v>
+        <v>2.391336</v>
       </c>
       <c r="AT242" t="n">
         <v>0</v>
@@ -38815,10 +38815,10 @@
         <v>0.00493645950017374</v>
       </c>
       <c r="J243" t="n">
-        <v>36606.0075188071</v>
+        <v>36629.4250303341</v>
       </c>
       <c r="K243" t="n">
-        <v>24913.9069143007</v>
+        <v>24919.1950811713</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -38920,7 +38920,7 @@
         <v>0</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.585224</v>
+        <v>1.594224</v>
       </c>
       <c r="AT243" t="n">
         <v>0</v>
@@ -38970,10 +38970,10 @@
         <v>0.00488530487992378</v>
       </c>
       <c r="J244" t="n">
-        <v>36947.8643318414</v>
+        <v>36971.500535228</v>
       </c>
       <c r="K244" t="n">
-        <v>25169.5242315104</v>
+        <v>25174.8666551073</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -39075,7 +39075,7 @@
         <v>0</v>
       </c>
       <c r="AS244" t="n">
-        <v>0.792612</v>
+        <v>0.797112</v>
       </c>
       <c r="AT244" t="n">
         <v>0</v>
@@ -39125,10 +39125,10 @@
         <v>0.00484625476688616</v>
       </c>
       <c r="J245" t="n">
-        <v>37297.4291901475</v>
+        <v>37321.2890163669</v>
       </c>
       <c r="K245" t="n">
-        <v>25431.9660393249</v>
+        <v>25437.3641681983</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -39280,10 +39280,10 @@
         <v>0.0048076557063792</v>
       </c>
       <c r="J246" t="n">
-        <v>37650.7980188476</v>
+        <v>37674.8839013671</v>
       </c>
       <c r="K246" t="n">
-        <v>25695.2107283869</v>
+        <v>25700.6647329545</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -39435,10 +39435,10 @@
         <v>0.00478086441968562</v>
       </c>
       <c r="J247" t="n">
-        <v>38008.2711313938</v>
+        <v>38032.5856957964</v>
       </c>
       <c r="K247" t="n">
-        <v>25965.0791877418</v>
+        <v>25970.5904739494</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -39590,10 +39590,10 @@
         <v>0.00473926501804089</v>
       </c>
       <c r="J248" t="n">
-        <v>38369.9486322701</v>
+        <v>38394.4945681775</v>
       </c>
       <c r="K248" t="n">
-        <v>26234.8472869407</v>
+        <v>26240.4158334861</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -39745,10 +39745,10 @@
         <v>0.00471315781573667</v>
       </c>
       <c r="J249" t="n">
-        <v>38735.8305214765</v>
+        <v>38760.6105185105</v>
       </c>
       <c r="K249" t="n">
-        <v>26506.6225892587</v>
+        <v>26512.248822186</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -39900,10 +39900,10 @@
         <v>0.00467984343253258</v>
       </c>
       <c r="J250" t="n">
-        <v>39105.3161721088</v>
+        <v>39130.3325356594</v>
       </c>
       <c r="K250" t="n">
-        <v>26781.0072556315</v>
+        <v>26786.6917287981</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -40055,10 +40055,10 @@
         <v>0.0046431744591946</v>
       </c>
       <c r="J251" t="n">
-        <v>39478.1052707148</v>
+        <v>39503.3601140561</v>
       </c>
       <c r="K251" t="n">
-        <v>27058.7038071506</v>
+        <v>27064.4472235295</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -40210,10 +40210,10 @@
         <v>0.00460321336856051</v>
       </c>
       <c r="J252" t="n">
-        <v>39854.5982352307</v>
+        <v>39880.0939277914</v>
       </c>
       <c r="K252" t="n">
-        <v>27339.5115235043</v>
+        <v>27345.3145434639</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -40365,10 +40365,10 @@
         <v>0.00457107075767049</v>
       </c>
       <c r="J253" t="n">
-        <v>40234.4947522043</v>
+        <v>40260.2334712972</v>
       </c>
       <c r="K253" t="n">
-        <v>27623.5307648484</v>
+        <v>27629.3940700595</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -40520,10 +40520,10 @@
         <v>0.00449893851450689</v>
       </c>
       <c r="J254" t="n">
-        <v>40615.3923140184</v>
+        <v>40641.3747000297</v>
       </c>
       <c r="K254" t="n">
-        <v>27909.8582897794</v>
+        <v>27915.7823701928</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -40675,10 +40675,10 @@
         <v>0.00453719183232471</v>
       </c>
       <c r="J255" t="n">
-        <v>41001.4953090032</v>
+        <v>41027.7246919406</v>
       </c>
       <c r="K255" t="n">
-        <v>28201.5049029759</v>
+        <v>28207.4908876085</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -40830,10 +40830,10 @@
         <v>0.00452033241158278</v>
       </c>
       <c r="J256" t="n">
-        <v>41390.4012295414</v>
+        <v>41416.8794024861</v>
       </c>
       <c r="K256" t="n">
-        <v>28496.5637614747</v>
+        <v>28502.6123746018</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -40985,10 +40985,10 @@
         <v>0.00449275624446099</v>
       </c>
       <c r="J257" t="n">
-        <v>41781.6095532127</v>
+        <v>41808.3379890528</v>
       </c>
       <c r="K257" t="n">
-        <v>28793.7301832485</v>
+        <v>28799.8418722165</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -41140,10 +41140,10 @@
         <v>0.00446545931210318</v>
       </c>
       <c r="J258" t="n">
-        <v>42175.2203845013</v>
+        <v>42202.2006201634</v>
       </c>
       <c r="K258" t="n">
-        <v>29092.8034479855</v>
+        <v>29098.9786175362</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -41295,10 +41295,10 @@
         <v>0.00443843729721394</v>
       </c>
       <c r="J259" t="n">
-        <v>42571.4339323752</v>
+        <v>42598.6676328633</v>
       </c>
       <c r="K259" t="n">
-        <v>29394.4860767771</v>
+        <v>29400.7252807681</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -41450,10 +41450,10 @@
         <v>0.00440811664554808</v>
       </c>
       <c r="J260" t="n">
-        <v>42970.3503013185</v>
+        <v>42997.839195675</v>
       </c>
       <c r="K260" t="n">
-        <v>29699.882031339</v>
+        <v>29706.1860579519</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
